--- a/Outcome/Appendix/figure_data/fig8.xlsx
+++ b/Outcome/Appendix/figure_data/fig8.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -226,9 +226,6 @@
   <si>
     <t xml:space="preserve">Streptococcus suis</t>
   </si>
-  <si>
-    <t xml:space="preserve">EM</t>
-  </si>
 </sst>
 </file>
 
@@ -283,8 +280,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M337" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M337"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M289" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M289"/>
   <tableColumns count="13">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="mean"/>
@@ -12435,1974 +12432,6 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B290" t="n">
-        <v>10.5658298943406</v>
-      </c>
-      <c r="C290" t="n">
-        <v>6.11771410961608</v>
-      </c>
-      <c r="D290" t="n">
-        <v>4.68618853906524</v>
-      </c>
-      <c r="E290" t="n">
-        <v>18.0177315003626</v>
-      </c>
-      <c r="F290" t="n">
-        <v>24.0188742208488</v>
-      </c>
-      <c r="G290" t="s">
-        <v>71</v>
-      </c>
-      <c r="H290" t="n">
-        <v>9</v>
-      </c>
-      <c r="I290" t="n">
-        <v>2</v>
-      </c>
-      <c r="J290" t="s">
-        <v>18</v>
-      </c>
-      <c r="K290" t="n">
-        <v>1.174</v>
-      </c>
-      <c r="L290" t="s">
-        <v>15</v>
-      </c>
-      <c r="M290" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B291" t="n">
-        <v>7.03366542313724</v>
-      </c>
-      <c r="C291" t="n">
-        <v>4.04894171425047</v>
-      </c>
-      <c r="D291" t="n">
-        <v>2.81266240260721</v>
-      </c>
-      <c r="E291" t="n">
-        <v>12.2306109724162</v>
-      </c>
-      <c r="F291" t="n">
-        <v>16.0114237137666</v>
-      </c>
-      <c r="G291" t="s">
-        <v>71</v>
-      </c>
-      <c r="H291" t="n">
-        <v>3</v>
-      </c>
-      <c r="I291" t="n">
-        <v>4</v>
-      </c>
-      <c r="J291" t="s">
-        <v>18</v>
-      </c>
-      <c r="K291" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="L291" t="s">
-        <v>15</v>
-      </c>
-      <c r="M291" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B292" t="n">
-        <v>6.00151016000826</v>
-      </c>
-      <c r="C292" t="n">
-        <v>3.23427513566829</v>
-      </c>
-      <c r="D292" t="n">
-        <v>2.22042432010748</v>
-      </c>
-      <c r="E292" t="n">
-        <v>11.2573473116677</v>
-      </c>
-      <c r="F292" t="n">
-        <v>14.8446188502267</v>
-      </c>
-      <c r="G292" t="s">
-        <v>71</v>
-      </c>
-      <c r="H292" t="n">
-        <v>5</v>
-      </c>
-      <c r="I292" t="n">
-        <v>1</v>
-      </c>
-      <c r="J292" t="s">
-        <v>18</v>
-      </c>
-      <c r="K292" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L292" t="s">
-        <v>15</v>
-      </c>
-      <c r="M292" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B293" t="n">
-        <v>5.30157110791404</v>
-      </c>
-      <c r="C293" t="n">
-        <v>2.77382397615364</v>
-      </c>
-      <c r="D293" t="n">
-        <v>1.85121307051691</v>
-      </c>
-      <c r="E293" t="n">
-        <v>10.0163610741809</v>
-      </c>
-      <c r="F293" t="n">
-        <v>13.3526609609061</v>
-      </c>
-      <c r="G293" t="s">
-        <v>71</v>
-      </c>
-      <c r="H293" t="n">
-        <v>5</v>
-      </c>
-      <c r="I293" t="n">
-        <v>0</v>
-      </c>
-      <c r="J293" t="s">
-        <v>18</v>
-      </c>
-      <c r="K293" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L293" t="s">
-        <v>15</v>
-      </c>
-      <c r="M293" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B294" t="n">
-        <v>7.12965339809904</v>
-      </c>
-      <c r="C294" t="n">
-        <v>3.7185030458613</v>
-      </c>
-      <c r="D294" t="n">
-        <v>2.55241899378886</v>
-      </c>
-      <c r="E294" t="n">
-        <v>13.4507636974873</v>
-      </c>
-      <c r="F294" t="n">
-        <v>19.10558262512</v>
-      </c>
-      <c r="G294" t="s">
-        <v>71</v>
-      </c>
-      <c r="H294" t="n">
-        <v>11</v>
-      </c>
-      <c r="I294" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J294" t="s">
-        <v>14</v>
-      </c>
-      <c r="K294" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="L294" t="s">
-        <v>15</v>
-      </c>
-      <c r="M294" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B295" t="n">
-        <v>6.26516529658246</v>
-      </c>
-      <c r="C295" t="n">
-        <v>3.13169462810249</v>
-      </c>
-      <c r="D295" t="n">
-        <v>2.12696988542874</v>
-      </c>
-      <c r="E295" t="n">
-        <v>12.1082401490315</v>
-      </c>
-      <c r="F295" t="n">
-        <v>16.4346289375377</v>
-      </c>
-      <c r="G295" t="s">
-        <v>71</v>
-      </c>
-      <c r="H295" t="n">
-        <v>3</v>
-      </c>
-      <c r="I295" t="n">
-        <v>3</v>
-      </c>
-      <c r="J295" t="s">
-        <v>18</v>
-      </c>
-      <c r="K295" t="n">
-        <v>2.085</v>
-      </c>
-      <c r="L295" t="s">
-        <v>15</v>
-      </c>
-      <c r="M295" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B296" t="n">
-        <v>8.08562214292285</v>
-      </c>
-      <c r="C296" t="n">
-        <v>3.93183029312526</v>
-      </c>
-      <c r="D296" t="n">
-        <v>2.66492487355952</v>
-      </c>
-      <c r="E296" t="n">
-        <v>16.359669358615</v>
-      </c>
-      <c r="F296" t="n">
-        <v>22.2709575420221</v>
-      </c>
-      <c r="G296" t="s">
-        <v>71</v>
-      </c>
-      <c r="H296" t="n">
-        <v>7</v>
-      </c>
-      <c r="I296" t="n">
-        <v>1</v>
-      </c>
-      <c r="J296" t="s">
-        <v>18</v>
-      </c>
-      <c r="K296" t="n">
-        <v>1.155</v>
-      </c>
-      <c r="L296" t="s">
-        <v>15</v>
-      </c>
-      <c r="M296" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B297" t="n">
-        <v>8.00414499177939</v>
-      </c>
-      <c r="C297" t="n">
-        <v>3.90045144242203</v>
-      </c>
-      <c r="D297" t="n">
-        <v>2.32349493921436</v>
-      </c>
-      <c r="E297" t="n">
-        <v>16.596002658408</v>
-      </c>
-      <c r="F297" t="n">
-        <v>24.2365216940089</v>
-      </c>
-      <c r="G297" t="s">
-        <v>71</v>
-      </c>
-      <c r="H297" t="n">
-        <v>3</v>
-      </c>
-      <c r="I297" t="n">
-        <v>5</v>
-      </c>
-      <c r="J297" t="s">
-        <v>18</v>
-      </c>
-      <c r="K297" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="L297" t="s">
-        <v>15</v>
-      </c>
-      <c r="M297" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B298" t="n">
-        <v>7.42074863398248</v>
-      </c>
-      <c r="C298" t="n">
-        <v>3.529537971357</v>
-      </c>
-      <c r="D298" t="n">
-        <v>2.05384548834748</v>
-      </c>
-      <c r="E298" t="n">
-        <v>15.6552266731273</v>
-      </c>
-      <c r="F298" t="n">
-        <v>21.4550108111135</v>
-      </c>
-      <c r="G298" t="s">
-        <v>71</v>
-      </c>
-      <c r="H298" t="n">
-        <v>6</v>
-      </c>
-      <c r="I298" t="n">
-        <v>1</v>
-      </c>
-      <c r="J298" t="s">
-        <v>18</v>
-      </c>
-      <c r="K298" t="n">
-        <v>1.236</v>
-      </c>
-      <c r="L298" t="s">
-        <v>15</v>
-      </c>
-      <c r="M298" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B299" t="n">
-        <v>7.73846309983948</v>
-      </c>
-      <c r="C299" t="n">
-        <v>3.58478098767772</v>
-      </c>
-      <c r="D299" t="n">
-        <v>2.35776375319069</v>
-      </c>
-      <c r="E299" t="n">
-        <v>16.9904780758691</v>
-      </c>
-      <c r="F299" t="n">
-        <v>27.2042030512069</v>
-      </c>
-      <c r="G299" t="s">
-        <v>71</v>
-      </c>
-      <c r="H299" t="n">
-        <v>7</v>
-      </c>
-      <c r="I299" t="n">
-        <v>1</v>
-      </c>
-      <c r="J299" t="s">
-        <v>18</v>
-      </c>
-      <c r="K299" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="L299" t="s">
-        <v>15</v>
-      </c>
-      <c r="M299" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B300" t="n">
-        <v>7.55034090576726</v>
-      </c>
-      <c r="C300" t="n">
-        <v>3.25507479157812</v>
-      </c>
-      <c r="D300" t="n">
-        <v>2.03190981673512</v>
-      </c>
-      <c r="E300" t="n">
-        <v>17.4095062779342</v>
-      </c>
-      <c r="F300" t="n">
-        <v>24.4045802805918</v>
-      </c>
-      <c r="G300" t="s">
-        <v>71</v>
-      </c>
-      <c r="H300" t="n">
-        <v>3</v>
-      </c>
-      <c r="I300" t="n">
-        <v>5</v>
-      </c>
-      <c r="J300" t="s">
-        <v>18</v>
-      </c>
-      <c r="K300" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="L300" t="s">
-        <v>15</v>
-      </c>
-      <c r="M300" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B301" t="n">
-        <v>5.7354433436491</v>
-      </c>
-      <c r="C301" t="n">
-        <v>2.51513634863627</v>
-      </c>
-      <c r="D301" t="n">
-        <v>1.5161126691908</v>
-      </c>
-      <c r="E301" t="n">
-        <v>12.8034826093851</v>
-      </c>
-      <c r="F301" t="n">
-        <v>18.8165431406048</v>
-      </c>
-      <c r="G301" t="s">
-        <v>71</v>
-      </c>
-      <c r="H301" t="n">
-        <v>4</v>
-      </c>
-      <c r="I301" t="n">
-        <v>2</v>
-      </c>
-      <c r="J301" t="s">
-        <v>18</v>
-      </c>
-      <c r="K301" t="n">
-        <v>1.433</v>
-      </c>
-      <c r="L301" t="s">
-        <v>15</v>
-      </c>
-      <c r="M301" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B302" t="n">
-        <v>8.29229232224369</v>
-      </c>
-      <c r="C302" t="n">
-        <v>3.19353829837781</v>
-      </c>
-      <c r="D302" t="n">
-        <v>1.8897223137314</v>
-      </c>
-      <c r="E302" t="n">
-        <v>20.4771248164026</v>
-      </c>
-      <c r="F302" t="n">
-        <v>31.510575431284</v>
-      </c>
-      <c r="G302" t="s">
-        <v>71</v>
-      </c>
-      <c r="H302" t="n">
-        <v>1</v>
-      </c>
-      <c r="I302" t="n">
-        <v>7</v>
-      </c>
-      <c r="J302" t="s">
-        <v>18</v>
-      </c>
-      <c r="K302" t="n">
-        <v>8.22</v>
-      </c>
-      <c r="L302" t="s">
-        <v>15</v>
-      </c>
-      <c r="M302" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B303" t="n">
-        <v>5.37443673219371</v>
-      </c>
-      <c r="C303" t="n">
-        <v>2.25385979396861</v>
-      </c>
-      <c r="D303" t="n">
-        <v>1.23188678724062</v>
-      </c>
-      <c r="E303" t="n">
-        <v>13.1191167498785</v>
-      </c>
-      <c r="F303" t="n">
-        <v>23.4175187461453</v>
-      </c>
-      <c r="G303" t="s">
-        <v>71</v>
-      </c>
-      <c r="H303" t="n">
-        <v>5</v>
-      </c>
-      <c r="I303" t="n">
-        <v>0</v>
-      </c>
-      <c r="J303" t="s">
-        <v>18</v>
-      </c>
-      <c r="K303" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="L303" t="s">
-        <v>15</v>
-      </c>
-      <c r="M303" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B304" t="n">
-        <v>4.74377042981353</v>
-      </c>
-      <c r="C304" t="n">
-        <v>1.8318062592449</v>
-      </c>
-      <c r="D304" t="n">
-        <v>0.900791742247508</v>
-      </c>
-      <c r="E304" t="n">
-        <v>11.606287660659</v>
-      </c>
-      <c r="F304" t="n">
-        <v>18.74893733577</v>
-      </c>
-      <c r="G304" t="s">
-        <v>71</v>
-      </c>
-      <c r="H304" t="n">
-        <v>3</v>
-      </c>
-      <c r="I304" t="n">
-        <v>2</v>
-      </c>
-      <c r="J304" t="s">
-        <v>18</v>
-      </c>
-      <c r="K304" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="L304" t="s">
-        <v>15</v>
-      </c>
-      <c r="M304" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B305" t="n">
-        <v>4.09141925371989</v>
-      </c>
-      <c r="C305" t="n">
-        <v>1.41281310207557</v>
-      </c>
-      <c r="D305" t="n">
-        <v>0.72555133067532</v>
-      </c>
-      <c r="E305" t="n">
-        <v>11.3155348949995</v>
-      </c>
-      <c r="F305" t="n">
-        <v>18.658817442763</v>
-      </c>
-      <c r="G305" t="s">
-        <v>71</v>
-      </c>
-      <c r="H305" t="n">
-        <v>6</v>
-      </c>
-      <c r="I305" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J305" t="s">
-        <v>14</v>
-      </c>
-      <c r="K305" t="n">
-        <v>0.682</v>
-      </c>
-      <c r="L305" t="s">
-        <v>15</v>
-      </c>
-      <c r="M305" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B306" t="n">
-        <v>5.44388895453095</v>
-      </c>
-      <c r="C306" t="n">
-        <v>1.9039031477862</v>
-      </c>
-      <c r="D306" t="n">
-        <v>0.881963406034688</v>
-      </c>
-      <c r="E306" t="n">
-        <v>14.9136522778701</v>
-      </c>
-      <c r="F306" t="n">
-        <v>27.4629866867704</v>
-      </c>
-      <c r="G306" t="s">
-        <v>71</v>
-      </c>
-      <c r="H306" t="n">
-        <v>3</v>
-      </c>
-      <c r="I306" t="n">
-        <v>2</v>
-      </c>
-      <c r="J306" t="s">
-        <v>18</v>
-      </c>
-      <c r="K306" t="n">
-        <v>1.812</v>
-      </c>
-      <c r="L306" t="s">
-        <v>15</v>
-      </c>
-      <c r="M306" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B307" t="n">
-        <v>4.87140101216112</v>
-      </c>
-      <c r="C307" t="n">
-        <v>1.68363227296962</v>
-      </c>
-      <c r="D307" t="n">
-        <v>0.852919942885296</v>
-      </c>
-      <c r="E307" t="n">
-        <v>13.1864627216411</v>
-      </c>
-      <c r="F307" t="n">
-        <v>22.4599090051608</v>
-      </c>
-      <c r="G307" t="s">
-        <v>71</v>
-      </c>
-      <c r="H307" t="n">
-        <v>2</v>
-      </c>
-      <c r="I307" t="n">
-        <v>3</v>
-      </c>
-      <c r="J307" t="s">
-        <v>18</v>
-      </c>
-      <c r="K307" t="n">
-        <v>2.429</v>
-      </c>
-      <c r="L307" t="s">
-        <v>15</v>
-      </c>
-      <c r="M307" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B308" t="n">
-        <v>6.11995310296688</v>
-      </c>
-      <c r="C308" t="n">
-        <v>1.89681078562048</v>
-      </c>
-      <c r="D308" t="n">
-        <v>0.859784896296416</v>
-      </c>
-      <c r="E308" t="n">
-        <v>17.7059756310562</v>
-      </c>
-      <c r="F308" t="n">
-        <v>27.8914354888754</v>
-      </c>
-      <c r="G308" t="s">
-        <v>71</v>
-      </c>
-      <c r="H308" t="n">
-        <v>5</v>
-      </c>
-      <c r="I308" t="n">
-        <v>1</v>
-      </c>
-      <c r="J308" t="s">
-        <v>18</v>
-      </c>
-      <c r="K308" t="n">
-        <v>1.224</v>
-      </c>
-      <c r="L308" t="s">
-        <v>15</v>
-      </c>
-      <c r="M308" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B309" t="n">
-        <v>6.29518384756131</v>
-      </c>
-      <c r="C309" t="n">
-        <v>1.85996744545281</v>
-      </c>
-      <c r="D309" t="n">
-        <v>0.762189759656465</v>
-      </c>
-      <c r="E309" t="n">
-        <v>19.8282086457612</v>
-      </c>
-      <c r="F309" t="n">
-        <v>34.0255984532178</v>
-      </c>
-      <c r="G309" t="s">
-        <v>71</v>
-      </c>
-      <c r="H309" t="n">
-        <v>4</v>
-      </c>
-      <c r="I309" t="n">
-        <v>2</v>
-      </c>
-      <c r="J309" t="s">
-        <v>18</v>
-      </c>
-      <c r="K309" t="n">
-        <v>1.572</v>
-      </c>
-      <c r="L309" t="s">
-        <v>15</v>
-      </c>
-      <c r="M309" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B310" t="n">
-        <v>5.79785491968343</v>
-      </c>
-      <c r="C310" t="n">
-        <v>1.69694515470787</v>
-      </c>
-      <c r="D310" t="n">
-        <v>0.712554100203047</v>
-      </c>
-      <c r="E310" t="n">
-        <v>18.0240987219703</v>
-      </c>
-      <c r="F310" t="n">
-        <v>31.4215784470406</v>
-      </c>
-      <c r="G310" t="s">
-        <v>71</v>
-      </c>
-      <c r="H310" t="n">
-        <v>3</v>
-      </c>
-      <c r="I310" t="n">
-        <v>3</v>
-      </c>
-      <c r="J310" t="s">
-        <v>18</v>
-      </c>
-      <c r="K310" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="L310" t="s">
-        <v>15</v>
-      </c>
-      <c r="M310" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B311" t="n">
-        <v>5.92748831233011</v>
-      </c>
-      <c r="C311" t="n">
-        <v>1.6969469347113</v>
-      </c>
-      <c r="D311" t="n">
-        <v>0.792164730542533</v>
-      </c>
-      <c r="E311" t="n">
-        <v>18.7793074006516</v>
-      </c>
-      <c r="F311" t="n">
-        <v>32.6518656511136</v>
-      </c>
-      <c r="G311" t="s">
-        <v>71</v>
-      </c>
-      <c r="H311" t="n">
-        <v>3</v>
-      </c>
-      <c r="I311" t="n">
-        <v>3</v>
-      </c>
-      <c r="J311" t="s">
-        <v>18</v>
-      </c>
-      <c r="K311" t="n">
-        <v>1.973</v>
-      </c>
-      <c r="L311" t="s">
-        <v>15</v>
-      </c>
-      <c r="M311" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B312" t="n">
-        <v>5.95164028448538</v>
-      </c>
-      <c r="C312" t="n">
-        <v>1.62784209942189</v>
-      </c>
-      <c r="D312" t="n">
-        <v>0.621834457427942</v>
-      </c>
-      <c r="E312" t="n">
-        <v>18.7234656726785</v>
-      </c>
-      <c r="F312" t="n">
-        <v>37.5984544445122</v>
-      </c>
-      <c r="G312" t="s">
-        <v>71</v>
-      </c>
-      <c r="H312" t="n">
-        <v>1</v>
-      </c>
-      <c r="I312" t="n">
-        <v>5</v>
-      </c>
-      <c r="J312" t="s">
-        <v>18</v>
-      </c>
-      <c r="K312" t="n">
-        <v>5.903</v>
-      </c>
-      <c r="L312" t="s">
-        <v>15</v>
-      </c>
-      <c r="M312" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B313" t="n">
-        <v>4.41817492290668</v>
-      </c>
-      <c r="C313" t="n">
-        <v>1.23969106630042</v>
-      </c>
-      <c r="D313" t="n">
-        <v>0.501730967709362</v>
-      </c>
-      <c r="E313" t="n">
-        <v>14.5656168624377</v>
-      </c>
-      <c r="F313" t="n">
-        <v>29.0680691879823</v>
-      </c>
-      <c r="G313" t="s">
-        <v>71</v>
-      </c>
-      <c r="H313" t="n">
-        <v>1</v>
-      </c>
-      <c r="I313" t="n">
-        <v>3</v>
-      </c>
-      <c r="J313" t="s">
-        <v>18</v>
-      </c>
-      <c r="K313" t="n">
-        <v>4.384</v>
-      </c>
-      <c r="L313" t="s">
-        <v>15</v>
-      </c>
-      <c r="M313" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B314" t="n">
-        <v>6.34528684419459</v>
-      </c>
-      <c r="C314" t="n">
-        <v>1.46634216085479</v>
-      </c>
-      <c r="D314" t="n">
-        <v>0.501655352599595</v>
-      </c>
-      <c r="E314" t="n">
-        <v>22.7207958388666</v>
-      </c>
-      <c r="F314" t="n">
-        <v>39.3482669558448</v>
-      </c>
-      <c r="G314" t="s">
-        <v>71</v>
-      </c>
-      <c r="H314" t="n">
-        <v>5</v>
-      </c>
-      <c r="I314" t="n">
-        <v>1</v>
-      </c>
-      <c r="J314" t="s">
-        <v>18</v>
-      </c>
-      <c r="K314" t="n">
-        <v>1.269</v>
-      </c>
-      <c r="L314" t="s">
-        <v>15</v>
-      </c>
-      <c r="M314" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B315" t="n">
-        <v>4.08999234026439</v>
-      </c>
-      <c r="C315" t="n">
-        <v>0.996398492737621</v>
-      </c>
-      <c r="D315" t="n">
-        <v>0.329697188285265</v>
-      </c>
-      <c r="E315" t="n">
-        <v>15.3263101770678</v>
-      </c>
-      <c r="F315" t="n">
-        <v>25.2110240596665</v>
-      </c>
-      <c r="G315" t="s">
-        <v>71</v>
-      </c>
-      <c r="H315" t="n">
-        <v>6</v>
-      </c>
-      <c r="I315" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J315" t="s">
-        <v>14</v>
-      </c>
-      <c r="K315" t="n">
-        <v>0.682</v>
-      </c>
-      <c r="L315" t="s">
-        <v>15</v>
-      </c>
-      <c r="M315" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B316" t="n">
-        <v>3.65980283608125</v>
-      </c>
-      <c r="C316" t="n">
-        <v>0.885163228358908</v>
-      </c>
-      <c r="D316" t="n">
-        <v>0.274935948127182</v>
-      </c>
-      <c r="E316" t="n">
-        <v>13.6155785262577</v>
-      </c>
-      <c r="F316" t="n">
-        <v>24.0351117581607</v>
-      </c>
-      <c r="G316" t="s">
-        <v>71</v>
-      </c>
-      <c r="H316" t="n">
-        <v>4</v>
-      </c>
-      <c r="I316" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" t="s">
-        <v>14</v>
-      </c>
-      <c r="K316" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="L316" t="s">
-        <v>15</v>
-      </c>
-      <c r="M316" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B317" t="n">
-        <v>3.10961014752019</v>
-      </c>
-      <c r="C317" t="n">
-        <v>0.604408347171293</v>
-      </c>
-      <c r="D317" t="n">
-        <v>0.210576269449475</v>
-      </c>
-      <c r="E317" t="n">
-        <v>11.9764282604358</v>
-      </c>
-      <c r="F317" t="n">
-        <v>25.8733526618083</v>
-      </c>
-      <c r="G317" t="s">
-        <v>71</v>
-      </c>
-      <c r="H317" t="n">
-        <v>3</v>
-      </c>
-      <c r="I317" t="n">
-        <v>0</v>
-      </c>
-      <c r="J317" t="s">
-        <v>18</v>
-      </c>
-      <c r="K317" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="L317" t="s">
-        <v>15</v>
-      </c>
-      <c r="M317" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B318" t="n">
-        <v>4.22927057452375</v>
-      </c>
-      <c r="C318" t="n">
-        <v>0.907228705267721</v>
-      </c>
-      <c r="D318" t="n">
-        <v>0.327921353657975</v>
-      </c>
-      <c r="E318" t="n">
-        <v>16.5827811735884</v>
-      </c>
-      <c r="F318" t="n">
-        <v>38.276451508341</v>
-      </c>
-      <c r="G318" t="s">
-        <v>71</v>
-      </c>
-      <c r="H318" t="n">
-        <v>5</v>
-      </c>
-      <c r="I318" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J318" t="s">
-        <v>14</v>
-      </c>
-      <c r="K318" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="L318" t="s">
-        <v>15</v>
-      </c>
-      <c r="M318" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B319" t="n">
-        <v>3.7986933585508</v>
-      </c>
-      <c r="C319" t="n">
-        <v>0.787015071464345</v>
-      </c>
-      <c r="D319" t="n">
-        <v>0.259241435686757</v>
-      </c>
-      <c r="E319" t="n">
-        <v>15.7572699042729</v>
-      </c>
-      <c r="F319" t="n">
-        <v>35.657121751661</v>
-      </c>
-      <c r="G319" t="s">
-        <v>71</v>
-      </c>
-      <c r="H319" t="n">
-        <v>15</v>
-      </c>
-      <c r="I319" t="n">
-        <v>-11</v>
-      </c>
-      <c r="J319" t="s">
-        <v>14</v>
-      </c>
-      <c r="K319" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="L319" t="s">
-        <v>15</v>
-      </c>
-      <c r="M319" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B320" t="n">
-        <v>4.70619195430485</v>
-      </c>
-      <c r="C320" t="n">
-        <v>0.935220826907971</v>
-      </c>
-      <c r="D320" t="n">
-        <v>0.305462291068557</v>
-      </c>
-      <c r="E320" t="n">
-        <v>20.3882209898145</v>
-      </c>
-      <c r="F320" t="n">
-        <v>45.2677319912956</v>
-      </c>
-      <c r="G320" t="s">
-        <v>71</v>
-      </c>
-      <c r="H320" t="n">
-        <v>5</v>
-      </c>
-      <c r="I320" t="n">
-        <v>0</v>
-      </c>
-      <c r="J320" t="s">
-        <v>14</v>
-      </c>
-      <c r="K320" t="n">
-        <v>0.941</v>
-      </c>
-      <c r="L320" t="s">
-        <v>15</v>
-      </c>
-      <c r="M320" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B321" t="n">
-        <v>4.64743895849751</v>
-      </c>
-      <c r="C321" t="n">
-        <v>0.876979053982938</v>
-      </c>
-      <c r="D321" t="n">
-        <v>0.248969449607374</v>
-      </c>
-      <c r="E321" t="n">
-        <v>20.6792476669137</v>
-      </c>
-      <c r="F321" t="n">
-        <v>48.6944008763247</v>
-      </c>
-      <c r="G321" t="s">
-        <v>71</v>
-      </c>
-      <c r="H321" t="n">
-        <v>7</v>
-      </c>
-      <c r="I321" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J321" t="s">
-        <v>14</v>
-      </c>
-      <c r="K321" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="L321" t="s">
-        <v>15</v>
-      </c>
-      <c r="M321" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B322" t="n">
-        <v>4.40963992073817</v>
-      </c>
-      <c r="C322" t="n">
-        <v>0.836546259369637</v>
-      </c>
-      <c r="D322" t="n">
-        <v>0.191887867125539</v>
-      </c>
-      <c r="E322" t="n">
-        <v>20.6143379543747</v>
-      </c>
-      <c r="F322" t="n">
-        <v>48.3053396485633</v>
-      </c>
-      <c r="G322" t="s">
-        <v>71</v>
-      </c>
-      <c r="H322" t="n">
-        <v>4</v>
-      </c>
-      <c r="I322" t="n">
-        <v>0</v>
-      </c>
-      <c r="J322" t="s">
-        <v>18</v>
-      </c>
-      <c r="K322" t="n">
-        <v>1.102</v>
-      </c>
-      <c r="L322" t="s">
-        <v>15</v>
-      </c>
-      <c r="M322" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B323" t="n">
-        <v>4.69081361673284</v>
-      </c>
-      <c r="C323" t="n">
-        <v>0.799904941316193</v>
-      </c>
-      <c r="D323" t="n">
-        <v>0.201398365449289</v>
-      </c>
-      <c r="E323" t="n">
-        <v>24.0940129440808</v>
-      </c>
-      <c r="F323" t="n">
-        <v>54.9606897401722</v>
-      </c>
-      <c r="G323" t="s">
-        <v>71</v>
-      </c>
-      <c r="H323" t="n">
-        <v>7</v>
-      </c>
-      <c r="I323" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J323" t="s">
-        <v>14</v>
-      </c>
-      <c r="K323" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="L323" t="s">
-        <v>15</v>
-      </c>
-      <c r="M323" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B324" t="n">
-        <v>4.61701997533601</v>
-      </c>
-      <c r="C324" t="n">
-        <v>0.74988026972051</v>
-      </c>
-      <c r="D324" t="n">
-        <v>0.183022800760918</v>
-      </c>
-      <c r="E324" t="n">
-        <v>22.2536185236865</v>
-      </c>
-      <c r="F324" t="n">
-        <v>60.5491703302923</v>
-      </c>
-      <c r="G324" t="s">
-        <v>71</v>
-      </c>
-      <c r="H324" t="n">
-        <v>7</v>
-      </c>
-      <c r="I324" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J324" t="s">
-        <v>14</v>
-      </c>
-      <c r="K324" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="L324" t="s">
-        <v>15</v>
-      </c>
-      <c r="M324" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B325" t="n">
-        <v>3.43759621837881</v>
-      </c>
-      <c r="C325" t="n">
-        <v>0.532091454326463</v>
-      </c>
-      <c r="D325" t="n">
-        <v>0.162208671363089</v>
-      </c>
-      <c r="E325" t="n">
-        <v>17.5658602867185</v>
-      </c>
-      <c r="F325" t="n">
-        <v>44.3176938503758</v>
-      </c>
-      <c r="G325" t="s">
-        <v>71</v>
-      </c>
-      <c r="H325" t="n">
-        <v>4</v>
-      </c>
-      <c r="I325" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J325" t="s">
-        <v>14</v>
-      </c>
-      <c r="K325" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L325" t="s">
-        <v>15</v>
-      </c>
-      <c r="M325" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B326" t="n">
-        <v>4.83361646779135</v>
-      </c>
-      <c r="C326" t="n">
-        <v>0.675260131571039</v>
-      </c>
-      <c r="D326" t="n">
-        <v>0.130082983194181</v>
-      </c>
-      <c r="E326" t="n">
-        <v>24.3147070091383</v>
-      </c>
-      <c r="F326" t="n">
-        <v>65.5651896578733</v>
-      </c>
-      <c r="G326" t="s">
-        <v>71</v>
-      </c>
-      <c r="H326" t="n">
-        <v>6</v>
-      </c>
-      <c r="I326" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J326" t="s">
-        <v>14</v>
-      </c>
-      <c r="K326" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="L326" t="s">
-        <v>15</v>
-      </c>
-      <c r="M326" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B327" t="n">
-        <v>3.25432742624468</v>
-      </c>
-      <c r="C327" t="n">
-        <v>0.423255919832488</v>
-      </c>
-      <c r="D327" t="n">
-        <v>0.0984826618367169</v>
-      </c>
-      <c r="E327" t="n">
-        <v>19.2221371239661</v>
-      </c>
-      <c r="F327" t="n">
-        <v>52.4793099264136</v>
-      </c>
-      <c r="G327" t="s">
-        <v>71</v>
-      </c>
-      <c r="H327" t="n">
-        <v>7</v>
-      </c>
-      <c r="I327" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J327" t="s">
-        <v>14</v>
-      </c>
-      <c r="K327" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="L327" t="s">
-        <v>15</v>
-      </c>
-      <c r="M327" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B328" t="n">
-        <v>2.92164712247686</v>
-      </c>
-      <c r="C328" t="n">
-        <v>0.372151635838863</v>
-      </c>
-      <c r="D328" t="n">
-        <v>0.0823873062984627</v>
-      </c>
-      <c r="E328" t="n">
-        <v>16.1665801122702</v>
-      </c>
-      <c r="F328" t="n">
-        <v>49.3235863092912</v>
-      </c>
-      <c r="G328" t="s">
-        <v>71</v>
-      </c>
-      <c r="H328" t="n">
-        <v>5</v>
-      </c>
-      <c r="I328" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J328" t="s">
-        <v>14</v>
-      </c>
-      <c r="K328" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="L328" t="s">
-        <v>15</v>
-      </c>
-      <c r="M328" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B329" t="n">
-        <v>2.48089979864907</v>
-      </c>
-      <c r="C329" t="n">
-        <v>0.309612596428488</v>
-      </c>
-      <c r="D329" t="n">
-        <v>0.0510540650805374</v>
-      </c>
-      <c r="E329" t="n">
-        <v>15.1570206722648</v>
-      </c>
-      <c r="F329" t="n">
-        <v>40.4155090598817</v>
-      </c>
-      <c r="G329" t="s">
-        <v>71</v>
-      </c>
-      <c r="H329" t="n">
-        <v>2</v>
-      </c>
-      <c r="I329" t="n">
-        <v>0</v>
-      </c>
-      <c r="J329" t="s">
-        <v>18</v>
-      </c>
-      <c r="K329" t="n">
-        <v>1.239</v>
-      </c>
-      <c r="L329" t="s">
-        <v>15</v>
-      </c>
-      <c r="M329" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B330" t="n">
-        <v>3.34399664932028</v>
-      </c>
-      <c r="C330" t="n">
-        <v>0.435017302327096</v>
-      </c>
-      <c r="D330" t="n">
-        <v>0.0680628069801823</v>
-      </c>
-      <c r="E330" t="n">
-        <v>21.4031560332073</v>
-      </c>
-      <c r="F330" t="n">
-        <v>58.3703815715633</v>
-      </c>
-      <c r="G330" t="s">
-        <v>71</v>
-      </c>
-      <c r="H330" t="n">
-        <v>5</v>
-      </c>
-      <c r="I330" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J330" t="s">
-        <v>14</v>
-      </c>
-      <c r="K330" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="L330" t="s">
-        <v>15</v>
-      </c>
-      <c r="M330" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B331" t="n">
-        <v>3.00496463767381</v>
-      </c>
-      <c r="C331" t="n">
-        <v>0.375431056174664</v>
-      </c>
-      <c r="D331" t="n">
-        <v>0.0756044510888437</v>
-      </c>
-      <c r="E331" t="n">
-        <v>18.8062411245704</v>
-      </c>
-      <c r="F331" t="n">
-        <v>56.4097070411416</v>
-      </c>
-      <c r="G331" t="s">
-        <v>71</v>
-      </c>
-      <c r="H331" t="n">
-        <v>1</v>
-      </c>
-      <c r="I331" t="n">
-        <v>2</v>
-      </c>
-      <c r="J331" t="s">
-        <v>18</v>
-      </c>
-      <c r="K331" t="n">
-        <v>2.985</v>
-      </c>
-      <c r="L331" t="s">
-        <v>15</v>
-      </c>
-      <c r="M331" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B332" t="n">
-        <v>3.75052735543746</v>
-      </c>
-      <c r="C332" t="n">
-        <v>0.447438852962873</v>
-      </c>
-      <c r="D332" t="n">
-        <v>0.0719838637760636</v>
-      </c>
-      <c r="E332" t="n">
-        <v>26.2567617148372</v>
-      </c>
-      <c r="F332" t="n">
-        <v>71.1263803519223</v>
-      </c>
-      <c r="G332" t="s">
-        <v>71</v>
-      </c>
-      <c r="H332" t="n">
-        <v>1</v>
-      </c>
-      <c r="I332" t="n">
-        <v>3</v>
-      </c>
-      <c r="J332" t="s">
-        <v>18</v>
-      </c>
-      <c r="K332" t="n">
-        <v>3.723</v>
-      </c>
-      <c r="L332" t="s">
-        <v>15</v>
-      </c>
-      <c r="M332" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B333" t="n">
-        <v>3.81136721636207</v>
-      </c>
-      <c r="C333" t="n">
-        <v>0.395657677973086</v>
-      </c>
-      <c r="D333" t="n">
-        <v>0.0772562470210947</v>
-      </c>
-      <c r="E333" t="n">
-        <v>25.0965691022159</v>
-      </c>
-      <c r="F333" t="n">
-        <v>72.0353006921187</v>
-      </c>
-      <c r="G333" t="s">
-        <v>71</v>
-      </c>
-      <c r="H333" t="n">
-        <v>5</v>
-      </c>
-      <c r="I333" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J333" t="s">
-        <v>14</v>
-      </c>
-      <c r="K333" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="L333" t="s">
-        <v>15</v>
-      </c>
-      <c r="M333" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B334" t="n">
-        <v>3.59654356161269</v>
-      </c>
-      <c r="C334" t="n">
-        <v>0.372310780320967</v>
-      </c>
-      <c r="D334" t="n">
-        <v>0.0468164944679887</v>
-      </c>
-      <c r="E334" t="n">
-        <v>24.5625995740268</v>
-      </c>
-      <c r="F334" t="n">
-        <v>66.5841641363464</v>
-      </c>
-      <c r="G334" t="s">
-        <v>71</v>
-      </c>
-      <c r="H334" t="n">
-        <v>0</v>
-      </c>
-      <c r="I334" t="n">
-        <v>4</v>
-      </c>
-      <c r="J334" t="s">
-        <v>18</v>
-      </c>
-      <c r="K334" t="n">
-        <v>360.654</v>
-      </c>
-      <c r="L334" t="s">
-        <v>68</v>
-      </c>
-      <c r="M334" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B335" t="n">
-        <v>3.67802189402242</v>
-      </c>
-      <c r="C335" t="n">
-        <v>0.354999965057155</v>
-      </c>
-      <c r="D335" t="n">
-        <v>0.0586173973196441</v>
-      </c>
-      <c r="E335" t="n">
-        <v>27.0095726696892</v>
-      </c>
-      <c r="F335" t="n">
-        <v>73.8066442273739</v>
-      </c>
-      <c r="G335" t="s">
-        <v>71</v>
-      </c>
-      <c r="H335" t="n">
-        <v>7</v>
-      </c>
-      <c r="I335" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J335" t="s">
-        <v>14</v>
-      </c>
-      <c r="K335" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="L335" t="s">
-        <v>15</v>
-      </c>
-      <c r="M335" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B336" t="n">
-        <v>3.69931306328101</v>
-      </c>
-      <c r="C336" t="n">
-        <v>0.339078465061202</v>
-      </c>
-      <c r="D336" t="n">
-        <v>0.0482844996932894</v>
-      </c>
-      <c r="E336" t="n">
-        <v>29.7584751754003</v>
-      </c>
-      <c r="F336" t="n">
-        <v>82.8083549350592</v>
-      </c>
-      <c r="G336" t="s">
-        <v>71</v>
-      </c>
-      <c r="H336" t="n">
-        <v>3</v>
-      </c>
-      <c r="I336" t="n">
-        <v>1</v>
-      </c>
-      <c r="J336" t="s">
-        <v>18</v>
-      </c>
-      <c r="K336" t="n">
-        <v>1.232</v>
-      </c>
-      <c r="L336" t="s">
-        <v>15</v>
-      </c>
-      <c r="M336" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B337" t="n">
-        <v>2.7407399123361</v>
-      </c>
-      <c r="C337" t="n">
-        <v>0.243036330379751</v>
-      </c>
-      <c r="D337" t="n">
-        <v>0.0424327430699729</v>
-      </c>
-      <c r="E337" t="n">
-        <v>22.2011472777366</v>
-      </c>
-      <c r="F337" t="n">
-        <v>74.6991542742331</v>
-      </c>
-      <c r="G337" t="s">
-        <v>71</v>
-      </c>
-      <c r="H337" t="n">
-        <v>3</v>
-      </c>
-      <c r="I337" t="n">
-        <v>0</v>
-      </c>
-      <c r="J337" t="s">
-        <v>14</v>
-      </c>
-      <c r="K337" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="L337" t="s">
-        <v>15</v>
-      </c>
-      <c r="M337" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
